--- a/SGC-CKN/Excel/fb970375-6493-48b5-8050-145270184fc4_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-44_D800_16-03-2026.xlsx
+++ b/SGC-CKN/Excel/fb970375-6493-48b5-8050-145270184fc4_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-44_D800_16-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P7-44</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>17-44</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -106,13 +106,10 @@
 16/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">03:50
@@ -174,7 +171,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:00
@@ -184,7 +181,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1.Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:50
@@ -194,9 +191,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">12:20
 16/03/2026</t>
   </si>
@@ -204,7 +198,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội, sỏi, sạn cát, đá khoảng, đa sắc, TT chặt đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">12:50
@@ -1230,24 +1224,24 @@
         <v>20.65</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-6.54</v>
@@ -1265,24 +1259,24 @@
         <v>15.05</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="E13" s="14" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="12">
         <v>-9.55</v>
@@ -1300,24 +1294,24 @@
         <v>4.97</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="E14" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>42</v>
       </c>
       <c r="F14" s="16">
         <v>-17.75</v>
@@ -1335,24 +1329,24 @@
         <v>2.84</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>44</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>45</v>
       </c>
       <c r="F15" s="19">
         <v>-21.3</v>
@@ -1370,24 +1364,24 @@
         <v>7.31</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>47</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>48</v>
       </c>
       <c r="F16" s="22">
         <v>-28</v>
@@ -1405,24 +1399,24 @@
         <v>2.9</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>50</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>51</v>
       </c>
       <c r="F17" s="25">
         <v>-35</v>
@@ -1440,24 +1434,24 @@
         <v>3.75</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>53</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>54</v>
       </c>
       <c r="F18" s="28">
         <v>-37.5</v>
@@ -1475,24 +1469,24 @@
         <v>1.8</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F19" s="31">
         <v>-39</v>
@@ -1510,24 +1504,24 @@
         <v>6.4</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F20" s="34">
         <v>-42.2</v>
@@ -1545,12 +1539,12 @@
         <v>5.38</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1656,31 +1650,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1720,7 +1714,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1749,7 +1743,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1778,7 +1772,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1807,7 +1801,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1836,7 +1830,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1865,7 +1859,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1894,7 +1888,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1923,7 +1917,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1952,7 +1946,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1975,13 +1969,13 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D12" s="39">
         <v>10</v>
